--- a/保存/output_results.xlsx
+++ b/保存/output_results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/higuchiyoshikazu/外部プロジェクト/AIHAT/ocr_for_gripglobe/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/higuchiyoshikazu/外部プロジェクト/AIHAT/ocr_for_gripglobe/保存/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE7FCEC-C078-5F45-8B15-1829A0F48E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B26CFBF8-D54C-7F49-AABB-6ACEAE01DA09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-12000" yWindow="500" windowWidth="11980" windowHeight="14340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22040" yWindow="0" windowWidth="22040" windowHeight="14840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="345">
   <si>
     <t>JSON全て</t>
   </si>
@@ -1101,6 +1101,14 @@
   </si>
   <si>
     <t>x(amount, invoice_registration_number)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>x(date, trading_partner, invoice_registration_number)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>x(date, invoice_registration_number)</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2200,6 +2208,9 @@
       <c r="H27" t="s">
         <v>18</v>
       </c>
+      <c r="I27" t="s">
+        <v>332</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
@@ -2226,6 +2237,9 @@
       <c r="H28" t="s">
         <v>18</v>
       </c>
+      <c r="I28" t="s">
+        <v>333</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
@@ -2249,6 +2263,9 @@
       <c r="H29" t="s">
         <v>11</v>
       </c>
+      <c r="I29" t="s">
+        <v>332</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
@@ -2275,6 +2292,9 @@
       <c r="H30" t="s">
         <v>18</v>
       </c>
+      <c r="I30" t="s">
+        <v>330</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
@@ -2301,6 +2321,9 @@
       <c r="H31" t="s">
         <v>18</v>
       </c>
+      <c r="I31" t="s">
+        <v>328</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
@@ -2327,8 +2350,11 @@
       <c r="H32" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="33" spans="1:8">
+      <c r="I32" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" t="s">
         <v>161</v>
       </c>
@@ -2353,8 +2379,11 @@
       <c r="H33" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="34" spans="1:8">
+      <c r="I33" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" t="s">
         <v>167</v>
       </c>
@@ -2376,8 +2405,11 @@
       <c r="H34" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="35" spans="1:8">
+      <c r="I34" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" t="s">
         <v>170</v>
       </c>
@@ -2402,8 +2434,11 @@
       <c r="H35" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="36" spans="1:8">
+      <c r="I35" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" t="s">
         <v>174</v>
       </c>
@@ -2425,8 +2460,11 @@
       <c r="H36" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="37" spans="1:8">
+      <c r="I36" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" t="s">
         <v>178</v>
       </c>
@@ -2445,8 +2483,11 @@
       <c r="H37" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="38" spans="1:8">
+      <c r="I37" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" t="s">
         <v>181</v>
       </c>
@@ -2468,8 +2509,11 @@
       <c r="H38" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="39" spans="1:8">
+      <c r="I38" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" t="s">
         <v>185</v>
       </c>
@@ -2494,8 +2538,11 @@
       <c r="H39" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="40" spans="1:8">
+      <c r="I39" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" t="s">
         <v>190</v>
       </c>
@@ -2520,8 +2567,11 @@
       <c r="H40" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="41" spans="1:8">
+      <c r="I40" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
       <c r="A41" t="s">
         <v>196</v>
       </c>
@@ -2546,8 +2596,11 @@
       <c r="H41" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="42" spans="1:8">
+      <c r="I41" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" t="s">
         <v>200</v>
       </c>
@@ -2572,8 +2625,11 @@
       <c r="H42" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="43" spans="1:8">
+      <c r="I42" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" t="s">
         <v>205</v>
       </c>
@@ -2598,8 +2654,11 @@
       <c r="H43" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="44" spans="1:8">
+      <c r="I43" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" t="s">
         <v>208</v>
       </c>
@@ -2624,8 +2683,11 @@
       <c r="H44" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="45" spans="1:8">
+      <c r="I44" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" t="s">
         <v>212</v>
       </c>
@@ -2650,8 +2712,11 @@
       <c r="H45" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="46" spans="1:8">
+      <c r="I45" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" t="s">
         <v>216</v>
       </c>
@@ -2676,8 +2741,11 @@
       <c r="H46" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="47" spans="1:8">
+      <c r="I46" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" t="s">
         <v>220</v>
       </c>
@@ -2702,8 +2770,11 @@
       <c r="H47" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="48" spans="1:8">
+      <c r="I47" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" t="s">
         <v>225</v>
       </c>
@@ -2728,8 +2799,11 @@
       <c r="H48" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="49" spans="1:8">
+      <c r="I48" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" t="s">
         <v>230</v>
       </c>
@@ -2754,8 +2828,11 @@
       <c r="H49" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="50" spans="1:8">
+      <c r="I49" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" t="s">
         <v>233</v>
       </c>
@@ -2780,8 +2857,11 @@
       <c r="H50" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="51" spans="1:8">
+      <c r="I50" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" t="s">
         <v>239</v>
       </c>
@@ -2806,8 +2886,11 @@
       <c r="H51" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="52" spans="1:8">
+      <c r="I51" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" t="s">
         <v>243</v>
       </c>
@@ -2832,8 +2915,11 @@
       <c r="H52" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="53" spans="1:8">
+      <c r="I52" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" t="s">
         <v>247</v>
       </c>
@@ -2858,8 +2944,11 @@
       <c r="H53" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="54" spans="1:8">
+      <c r="I53" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" t="s">
         <v>252</v>
       </c>
@@ -2878,8 +2967,11 @@
       <c r="H54" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="55" spans="1:8">
+      <c r="I54" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" t="s">
         <v>255</v>
       </c>
@@ -2904,8 +2996,11 @@
       <c r="H55" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="56" spans="1:8">
+      <c r="I55" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" t="s">
         <v>261</v>
       </c>
@@ -2930,8 +3025,11 @@
       <c r="H56" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="57" spans="1:8">
+      <c r="I56" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
       <c r="A57" t="s">
         <v>267</v>
       </c>
@@ -2953,8 +3051,11 @@
       <c r="H57" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="58" spans="1:8">
+      <c r="I57" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58" t="s">
         <v>272</v>
       </c>
@@ -2976,8 +3077,11 @@
       <c r="H58" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="59" spans="1:8">
+      <c r="I58" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
       <c r="A59" t="s">
         <v>276</v>
       </c>
@@ -2999,8 +3103,11 @@
       <c r="H59" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="60" spans="1:8">
+      <c r="I59" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
       <c r="A60" t="s">
         <v>281</v>
       </c>
@@ -3019,8 +3126,11 @@
       <c r="H60" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="61" spans="1:8">
+      <c r="I60" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61" t="s">
         <v>285</v>
       </c>
@@ -3045,8 +3155,11 @@
       <c r="H61" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="62" spans="1:8">
+      <c r="I61" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
       <c r="A62" t="s">
         <v>291</v>
       </c>
@@ -3068,8 +3181,11 @@
       <c r="H62" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="63" spans="1:8">
+      <c r="I62" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
       <c r="A63" t="s">
         <v>296</v>
       </c>
@@ -3094,8 +3210,11 @@
       <c r="H63" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="64" spans="1:8">
+      <c r="I63" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
       <c r="A64" t="s">
         <v>302</v>
       </c>
@@ -3120,8 +3239,11 @@
       <c r="H64" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="65" spans="1:8">
+      <c r="I64" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
       <c r="A65" t="s">
         <v>307</v>
       </c>
@@ -3143,8 +3265,11 @@
       <c r="H65" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="66" spans="1:8">
+      <c r="I65" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
       <c r="A66" t="s">
         <v>312</v>
       </c>
@@ -3166,8 +3291,11 @@
       <c r="H66" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="67" spans="1:8">
+      <c r="I66" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
       <c r="A67" t="s">
         <v>317</v>
       </c>
@@ -3189,8 +3317,11 @@
       <c r="H67" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="68" spans="1:8">
+      <c r="I67" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
       <c r="A68" t="s">
         <v>321</v>
       </c>
@@ -3214,6 +3345,9 @@
       </c>
       <c r="H68" t="s">
         <v>18</v>
+      </c>
+      <c r="I68" t="s">
+        <v>328</v>
       </c>
     </row>
   </sheetData>
